--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10512"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hastingj/Work/Onto/addiction-ontology/imports/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bgehrk/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64F957F5-2BA0-B14F-A973-B8AE86A68AAA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{336AA84B-5ABF-0541-B3F6-50E6C1561539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="14580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="25600" windowHeight="14580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Imports" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="93">
   <si>
     <t>Ontology ID</t>
   </si>
@@ -259,15 +259,6 @@
   </si>
   <si>
     <t>Carcinogen [CHEBI:50903];Alcohol dehydrogenase 1B [CHEBI:50269]; Flavouring agent [CHEBI:35617]; nicotinic acetylcholine receptor agonist [CHEBI:47958]; nicotinic antagonist [CHEBI:48878]; carcinogenic agent [CHEBI:50903]; cannabinoid receptor agonist [CHEBI:67072]; cb1 receptor antagonist [CHEBI:73416]; cb2 receptor agonist [CHEBI:73417]</t>
-  </si>
-  <si>
-    <t>ERO</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/ero.owl</t>
-  </si>
-  <si>
-    <t>intubation [ERO:0001108]</t>
   </si>
   <si>
     <t>﻿Antidepressant drug [CHEBI:35469];Antimanic drug [CHEBI:35477];Antipsychotic drug [CHEBI:35476];Anxiolytic drug [CHEBI:35474];Central nervous system depressent [CHEBI:35488];Central nervous system drug [CHEBI:35470];Pharmaceutical [CHEBI:52217];Tranquilizing drug  [CHEBI:35473];Drug [CHEBI:23888]; psychotropic drug [CHEBI:35471]; opioid analgesic [CHEBI:35482]; antitussive [CHEBI:51177]</t>
@@ -368,20 +359,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -403,9 +387,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -443,7 +427,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -549,7 +533,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -691,7 +675,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -699,37 +683,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
     <col min="2" max="2" width="52.1640625" customWidth="1"/>
     <col min="3" max="3" width="27.6640625" customWidth="1"/>
     <col min="4" max="4" width="54" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:6" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="3" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>32</v>
       </c>
@@ -742,32 +725,32 @@
       <c r="D2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" t="s">
         <v>40</v>
       </c>
       <c r="F2"/>
     </row>
-    <row r="3" spans="1:6" s="3" customFormat="1" ht="204" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:6" s="2" customFormat="1" ht="204" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" s="7" t="s">
+      <c r="B3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="3" customFormat="1" ht="136" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" s="2" customFormat="1" ht="136" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -778,14 +761,14 @@
         <v>19</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" t="s">
         <v>40</v>
       </c>
       <c r="F4"/>
     </row>
-    <row r="5" spans="1:6" s="3" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -798,63 +781,63 @@
       <c r="D5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" t="s">
         <v>41</v>
       </c>
       <c r="F5"/>
     </row>
-    <row r="6" spans="1:6" s="3" customFormat="1" ht="102" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:6" s="2" customFormat="1" ht="102" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="388" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+      <c r="A7" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="D7" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E7" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="3"/>
+      <c r="F7" s="2"/>
     </row>
     <row r="8" spans="1:6" ht="136" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+      <c r="A8" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="D8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" t="s">
         <v>41</v>
       </c>
-      <c r="F8" s="3"/>
+      <c r="F8" s="2"/>
     </row>
     <row r="9" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -869,7 +852,7 @@
       <c r="D9" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" t="s">
         <v>40</v>
       </c>
     </row>
@@ -884,9 +867,9 @@
         <v>49</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" t="s">
         <v>41</v>
       </c>
     </row>
@@ -901,288 +884,271 @@
         <v>19</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="85" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="51" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="2"/>
+    </row>
+    <row r="17" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" t="s">
+        <v>19</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>52</v>
+      </c>
+      <c r="B20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="17" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>46</v>
+      </c>
+      <c r="B21" t="s">
+        <v>47</v>
+      </c>
+      <c r="C21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="51" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="102" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>16</v>
+      </c>
+      <c r="B24" t="s">
+        <v>17</v>
+      </c>
+      <c r="C24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="102" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B25" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>76</v>
-      </c>
-      <c r="B12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>58</v>
-      </c>
-      <c r="B15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" t="s">
-        <v>19</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" t="s">
-        <v>83</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B19" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" t="s">
-        <v>19</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="102" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" t="s">
-        <v>19</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" t="s">
-        <v>87</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="102" x14ac:dyDescent="0.2">
+      <c r="E25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="34" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B26" t="s">
         <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>63</v>
-      </c>
-      <c r="B27" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" t="s">
-        <v>64</v>
-      </c>
-      <c r="D27" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E26" t="s">
         <v>40</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:F27">
-    <sortCondition ref="A2:A27"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F26">
+    <sortCondition ref="A2:A26"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bgehrk/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C19C7846-0687-7640-8479-1F7290795A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9080D8E9-CE14-F448-BEE8-CD67949D60E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1680" windowWidth="25600" windowHeight="14580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="3420" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Imports" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="115">
   <si>
     <t>Ontology ID</t>
   </si>
@@ -73,7 +73,7 @@
     <t>http://purl.obolibrary.org/obo/bfo.owl</t>
   </si>
   <si>
-    <t>process [BFO:0000015]; object aggregate [BFO:0000027]; role [BFO:0000023]; disposition [BFO:0000016]; object [BFO:0000030]; process profile [BFO:0000144]; site [BFO:0000029]; occurrent [BFO:0000003]; process boundary [BFO:0000035]; temporal region [BFO:0000008]; fiat object part [﻿BFO:0000024]; immaterial entity [BFO:0000141]; ﻿spatial region [BFO:0000006];specifically dependent continuant [BFO:0000020]</t>
+    <t>﻿spatial region [BFO:0000006]; object [BFO:0000030]; occurrent [BFO:0000003]; fiat object part [﻿BFO:0000024]; process [BFO:0000015]; site [BFO:0000029]; role [BFO:0000023]; fiat object [BFO:0000024]; immaterial entity [BFO:0000141]; object aggregate [BFO:0000027]; temporal region [BFO:0000008]; disposition [BFO:0000016]; process boundary [BFO:0000035]; process profile [BFO:0000144]; specifically dependent continuant [BFO:0000020]</t>
   </si>
   <si>
     <t>BFO-DEV</t>
@@ -202,7 +202,7 @@
     <t>http://purl.obolibrary.org/obo/obcs.owl</t>
   </si>
   <si>
-    <t>Credible interval [OBCS:0000071]; Mortality ratio [OBCS:0000150]; model [OBCS:0000035]</t>
+    <t>Mortality ratio [OBCS:0000150]; Credible interval [OBCS:0000071]; mortality ratio [OBCS:0000150]; model [OBCS:0000035]</t>
   </si>
   <si>
     <t>OBI</t>
@@ -331,7 +331,7 @@
     <t>CHEBI</t>
   </si>
   <si>
-    <t>cotinine [CHEBI:68641]; acetaldehyde [CHEBI:15343]; acrolein [CHEBI:15368]; acrylonitrile [CHEBI:28217]; metabolite [CHEBI:25212]; 4-(methylnitrosamino)-1-(3-pyridyl)-1-butanol [CHEBI:82569]; acetylcysteine [CHEBI:22198]; aripiprazole [CHEBI:31236]; methanol [CHEBI:17790]</t>
+    <t>CB2 receptor agonist [CHEBI:73417]; methanol [CHEBI:17790]; acetaldehyde [CHEBI:15343]; carbon-monoxide [CHEBI:17245]; methadrone [CHEBI:59331]; aripiprazole [CHEBI:31236]; alcohol dehydrogenase 1B [CHEBI:50269]; cotinine [CHEBI:68641]; drug role [CHEBI:23888]; acrolein [CHEBI:15368]; 3,4-Methylenedioxymethamphetamine [CHEBI:1391]; 4-(methylnitrosamino)-1-(3-pyridyl)-1-butanol [CHEBI:82569]; tetrahydrocannabinol [CHEBI:66964]; antipsychotic drug [CHEBI:35476]; acrylonitrile [CHEBI:28217]; metabolite [CHEBI:25212]; codeine [CHEBI:38164]; acetylcysteine [CHEBI:22198]</t>
   </si>
   <si>
     <t>UBERON</t>
@@ -340,13 +340,31 @@
     <t>death [UBERON:0035944]</t>
   </si>
   <si>
-    <t>GSSO</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/gsso.owl</t>
-  </si>
-  <si>
-    <t>advocacy organisation [GSSO:005379]; health organisation [GSSO:007328]; human rights organisation [GSSO:003501]; non-profit organisation [GSSO:004615]</t>
+    <t>SDGIO</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/SDG-InterfaceOntology/sdgio/master/sdgio.owl</t>
+  </si>
+  <si>
+    <t>unemployed status [SDGIO:00010026]</t>
+  </si>
+  <si>
+    <t>"SDGIO: http://purl.unep.org/sdg/SDGIO_"</t>
+  </si>
+  <si>
+    <t>SIO</t>
+  </si>
+  <si>
+    <t>http://semanticscience.org/ontology/sio.owl</t>
+  </si>
+  <si>
+    <t>geographic region [SIO:000414]</t>
+  </si>
+  <si>
+    <t>geographic region [SIO:000414]; geolegal region [SIO:000413]; geopolitical region [SIO:000415]</t>
+  </si>
+  <si>
+    <t>"SIO: http://semanticscience.org/resource/SIO_"</t>
   </si>
 </sst>
 </file>
@@ -720,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -1281,6 +1299,29 @@
       <c r="E32" t="s">
         <v>10</v>
       </c>
+      <c r="F32" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" t="s">
+        <v>112</v>
+      </c>
+      <c r="D33" t="s">
+        <v>113</v>
+      </c>
+      <c r="E33" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" t="s">
+        <v>114</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bgehrk/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9080D8E9-CE14-F448-BEE8-CD67949D60E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27BEF9C4-8C9D-5C40-B6D0-4112AB44C042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="3420" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="112">
   <si>
     <t>Ontology ID</t>
   </si>
@@ -149,15 +149,6 @@
   </si>
   <si>
     <t>building [ENVO:00000073]; commercial building [ENVO:01001222]; environmental system [ENVO:01000254]; fire [ENVO:01000786]; environmental disposition [ENVO:01000452]; environmental material [ENVO:00010483]; construction [ENVO:01001813]; smoke [ENVO:01000838]; laboratory facility [ENVO:01001406]; ﻿human construction [ENVO:00000070]; shop [ENVO:00002221]; aerosol [ENVO:00010505]</t>
-  </si>
-  <si>
-    <t>ERO</t>
-  </si>
-  <si>
-    <t>https://data.bioontology.org/ontologies/ERO/submissions/14/download?apikey=8b5b7825-538d-40e0-9e9e-5ab9274a9aeb</t>
-  </si>
-  <si>
-    <t>intubation [ERO:0001108]</t>
   </si>
   <si>
     <t>IAO</t>
@@ -738,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -942,7 +933,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" ht="85" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>43</v>
       </c>
@@ -950,16 +941,16 @@
         <v>44</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>45</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>46</v>
       </c>
@@ -976,7 +967,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>49</v>
       </c>
@@ -993,7 +984,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -1003,14 +994,14 @@
       <c r="C15" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" t="s">
         <v>54</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>55</v>
       </c>
@@ -1020,12 +1011,13 @@
       <c r="C16" t="s">
         <v>8</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="F16" s="2"/>
     </row>
     <row r="17" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
@@ -1043,9 +1035,8 @@
       <c r="E17" t="s">
         <v>10</v>
       </c>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>61</v>
       </c>
@@ -1053,24 +1044,24 @@
         <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>67</v>
@@ -1079,7 +1070,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>68</v>
       </c>
@@ -1087,41 +1078,41 @@
         <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>8</v>
+        <v>70</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
-        <v>77</v>
+        <v>8</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>78</v>
@@ -1130,7 +1121,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:6" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -1147,7 +1138,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="102" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>82</v>
       </c>
@@ -1155,38 +1146,38 @@
         <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D24" s="1" t="s">
         <v>84</v>
       </c>
+      <c r="D24" t="s">
+        <v>85</v>
+      </c>
       <c r="E24" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="102" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B25" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>90</v>
+      </c>
+      <c r="B26" t="s">
         <v>87</v>
-      </c>
-      <c r="D25" t="s">
-        <v>88</v>
-      </c>
-      <c r="E25" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="102" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>89</v>
-      </c>
-      <c r="B26" t="s">
-        <v>90</v>
       </c>
       <c r="C26" t="s">
         <v>91</v>
@@ -1198,17 +1189,17 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="34" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>93</v>
       </c>
       <c r="B27" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>94</v>
-      </c>
-      <c r="D27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" t="s">
         <v>95</v>
       </c>
       <c r="E27" t="s">
@@ -1237,13 +1228,13 @@
         <v>99</v>
       </c>
       <c r="B29" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" t="s">
         <v>100</v>
-      </c>
-      <c r="C29" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" t="s">
-        <v>101</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
@@ -1251,16 +1242,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>101</v>
+      </c>
+      <c r="B30" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" t="s">
         <v>102</v>
-      </c>
-      <c r="B30" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" t="s">
-        <v>27</v>
-      </c>
-      <c r="D30" t="s">
-        <v>103</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -1268,10 +1259,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>103</v>
+      </c>
+      <c r="B31" t="s">
         <v>104</v>
-      </c>
-      <c r="B31" t="s">
-        <v>90</v>
       </c>
       <c r="C31" t="s">
         <v>8</v>
@@ -1282,45 +1273,28 @@
       <c r="E31" t="s">
         <v>10</v>
       </c>
+      <c r="F31" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B32" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C32" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="D32" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>110</v>
-      </c>
-      <c r="B33" t="s">
         <v>111</v>
-      </c>
-      <c r="C33" t="s">
-        <v>112</v>
-      </c>
-      <c r="D33" t="s">
-        <v>113</v>
-      </c>
-      <c r="E33" t="s">
-        <v>10</v>
-      </c>
-      <c r="F33" t="s">
-        <v>114</v>
       </c>
     </row>
   </sheetData>
